--- a/data/final/estimations/2018_cbcr_etr_rates_new.xlsx
+++ b/data/final/estimations/2018_cbcr_etr_rates_new.xlsx
@@ -594,11 +594,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5018127880415215</v>
+        <v>0.5482325278934045</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.5018127880415215</v>
+        <v>0.5482325278934045</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -923,13 +923,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.00528506624336367</v>
+        <v>0.008428414063221973</v>
       </c>
       <c r="C29" t="n">
         <v>0.008072629609230664</v>
       </c>
       <c r="D29" t="n">
-        <v>0.005420747105050998</v>
+        <v>0.008401574074649708</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -978,11 +978,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.008166301351291658</v>
+        <v>0.01266334614764634</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
-        <v>0.008166301351291658</v>
+        <v>0.01266334614764634</v>
       </c>
       <c r="E32" t="n">
         <v>0.25</v>
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.07443771615712873</v>
+        <v>0.1005817932163082</v>
       </c>
       <c r="C38" t="n">
         <v>0.1262436700329104</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0899556782310134</v>
+        <v>0.1099796111010298</v>
       </c>
       <c r="E38" t="n">
         <v>0.2114900052547455</v>
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.01344183365270377</v>
+        <v>0.01966609925737078</v>
       </c>
       <c r="C49" t="n">
-        <v>0.05386610950290214</v>
+        <v>0.03501297117688639</v>
       </c>
       <c r="D49" t="n">
-        <v>0.01866363881292328</v>
+        <v>0.02350755745183776</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -1292,11 +1292,11 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.02905041331086948</v>
+        <v>0.0370258066257404</v>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
-        <v>0.02905041331086948</v>
+        <v>0.0370258066257404</v>
       </c>
       <c r="E50" t="n">
         <v>0.125</v>
@@ -1878,13 +1878,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.06592727440070931</v>
+        <v>0.07232803956820501</v>
       </c>
       <c r="C84" t="n">
         <v>0.05174930477244143</v>
       </c>
       <c r="D84" t="n">
-        <v>0.06084791936767611</v>
+        <v>0.06451165932026172</v>
       </c>
       <c r="E84" t="n">
         <v>0.1650000065565109</v>
@@ -1948,11 +1948,11 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.1370908919113721</v>
+        <v>0.1581612562462731</v>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="n">
-        <v>0.1370908919113721</v>
+        <v>0.1581612562462731</v>
       </c>
       <c r="E88" t="n">
         <v>0.0900000035762787</v>
@@ -1968,10 +1968,10 @@
         <v>0.2674779579077783</v>
       </c>
       <c r="C89" t="n">
-        <v>0.4841503920493467</v>
+        <v>0.274697664954085</v>
       </c>
       <c r="D89" t="n">
-        <v>0.462739096949885</v>
+        <v>0.2701306676337006</v>
       </c>
       <c r="E89" t="n">
         <v>0.25</v>
@@ -2022,13 +2022,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.112997252968767</v>
+        <v>0.1631190612032202</v>
       </c>
       <c r="C92" t="n">
-        <v>0.03063916777041436</v>
+        <v>0.01991545905076934</v>
       </c>
       <c r="D92" t="n">
-        <v>0.09796877883325807</v>
+        <v>0.115658017671716</v>
       </c>
       <c r="E92" t="n">
         <v>0.125</v>
@@ -2112,10 +2112,10 @@
         <v>0.2438601733506817</v>
       </c>
       <c r="C97" t="n">
-        <v>0.1869176142861273</v>
+        <v>0.2317778417147978</v>
       </c>
       <c r="D97" t="n">
-        <v>0.2120676164112788</v>
+        <v>0.237760824316831</v>
       </c>
       <c r="E97" t="n">
         <v>0.2780599892139435</v>
@@ -2457,13 +2457,13 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.02674514102117078</v>
+        <v>0.03687119029011863</v>
       </c>
       <c r="C117" t="n">
-        <v>0.008345715653869103</v>
+        <v>0.01283956254441401</v>
       </c>
       <c r="D117" t="n">
-        <v>0.02339023467513469</v>
+        <v>0.03286877930124139</v>
       </c>
       <c r="E117" t="n">
         <v>0.2601000070571899</v>
@@ -2493,11 +2493,11 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.3054436963474889</v>
+        <v>0.3431331842597418</v>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="n">
-        <v>0.3054436963474889</v>
+        <v>0.3431331842597418</v>
       </c>
       <c r="E119" t="n">
         <v>0.119999997317791</v>
@@ -2782,11 +2782,11 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.05533522242525027</v>
+        <v>0.06832391353362346</v>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="n">
-        <v>0.05533522242525027</v>
+        <v>0.06832391353362346</v>
       </c>
       <c r="E136" t="n">
         <v>0.1500000059604645</v>
@@ -2903,13 +2903,13 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.03672145299137798</v>
+        <v>0.04237689805304731</v>
       </c>
       <c r="C143" t="n">
         <v>0.1497323306832883</v>
       </c>
       <c r="D143" t="n">
-        <v>0.04865285157042064</v>
+        <v>0.05524752335770206</v>
       </c>
       <c r="E143" t="n">
         <v>0.25</v>
@@ -3175,11 +3175,11 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.01704718331377299</v>
+        <v>0.0277049856528661</v>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="n">
-        <v>0.01704718331377299</v>
+        <v>0.0277049856528661</v>
       </c>
       <c r="E159" t="n">
         <v>0.39</v>
@@ -3366,13 +3366,13 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.05246449770985217</v>
+        <v>0.07631584368089703</v>
       </c>
       <c r="C170" t="n">
         <v>0.1896598339380842</v>
       </c>
       <c r="D170" t="n">
-        <v>0.06953090356955129</v>
+        <v>0.09572735811429038</v>
       </c>
       <c r="E170" t="n">
         <v>0.1700000017881393</v>
@@ -3541,10 +3541,10 @@
         <v>0.1471577486317217</v>
       </c>
       <c r="C180" t="n">
-        <v>0.163833433100592</v>
+        <v>0.2000509994614199</v>
       </c>
       <c r="D180" t="n">
-        <v>0.1576681194632991</v>
+        <v>0.1779765147101586</v>
       </c>
       <c r="E180" t="n">
         <v>0.2199999988079071</v>
@@ -3815,10 +3815,10 @@
         <v>0.09197695807867363</v>
       </c>
       <c r="C196" t="n">
-        <v>0.1956348403887919</v>
+        <v>0.3085010944592488</v>
       </c>
       <c r="D196" t="n">
-        <v>0.1673399007613276</v>
+        <v>0.2279799551263891</v>
       </c>
       <c r="E196" t="n">
         <v>0.27</v>

--- a/data/final/estimations/2018_cbcr_etr_rates_new.xlsx
+++ b/data/final/estimations/2018_cbcr_etr_rates_new.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E209"/>
+  <dimension ref="A1:E208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,11 +662,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08831027468328029</v>
+        <v>0.0871061780573317</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.08831027468328029</v>
+        <v>0.0871061780573317</v>
       </c>
       <c r="E14" t="n">
         <v>0.27</v>
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1838851456537264</v>
+        <v>0.1838492350767729</v>
       </c>
       <c r="C16" t="n">
         <v>0.3749053576605499</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2995362513929005</v>
+        <v>0.2995131684849566</v>
       </c>
       <c r="E16" t="n">
         <v>0.300000011920929</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1163171828332292</v>
+        <v>0.1163212569057596</v>
       </c>
       <c r="C17" t="n">
         <v>0.09033945599052512</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1055741182229227</v>
+        <v>0.1055766913237821</v>
       </c>
       <c r="E17" t="n">
         <v>0.25</v>
@@ -855,11 +855,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.01492877504978708</v>
+        <v>0.0001130174453552384</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
-        <v>0.01492877504978708</v>
+        <v>0.0001130174453552384</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.1794106098526372</v>
+        <v>0.17941070761734</v>
       </c>
       <c r="C37" t="n">
         <v>0.1641608651554682</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1698171953329929</v>
+        <v>0.1698172296561839</v>
       </c>
       <c r="E37" t="n">
         <v>0.2680000066757202</v>
@@ -1120,11 +1120,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.1903317454825871</v>
+        <v>0.1903311494800958</v>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
-        <v>0.1903317454825871</v>
+        <v>0.1903311494800958</v>
       </c>
       <c r="E40" t="n">
         <v>0.25</v>
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.01966609925737078</v>
+        <v>0.01966626387433586</v>
       </c>
       <c r="C49" t="n">
         <v>0.03501297117688639</v>
       </c>
       <c r="D49" t="n">
-        <v>0.02350755745183776</v>
+        <v>0.02350770496994507</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -1381,11 +1381,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5111394147495351</v>
+        <v>0.5117401816797207</v>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
-        <v>0.5111394147495351</v>
+        <v>0.5117401816797207</v>
       </c>
       <c r="E55" t="n">
         <v>0.26</v>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.1251684094558713</v>
+        <v>0.1251669830632952</v>
       </c>
       <c r="C58" t="n">
         <v>0.1856941285725743</v>
       </c>
       <c r="D58" t="n">
-        <v>0.1516264640550345</v>
+        <v>0.151625491478223</v>
       </c>
       <c r="E58" t="n">
         <v>0.25</v>
@@ -1536,11 +1536,11 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.1213667303258556</v>
+        <v>0.1213712153034949</v>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
-        <v>0.1213667303258556</v>
+        <v>0.1213712153034949</v>
       </c>
       <c r="E64" t="inlineStr"/>
     </row>
@@ -1551,13 +1551,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.2038944137107646</v>
+        <v>0.2040745592859039</v>
       </c>
       <c r="C65" t="n">
         <v>0.2480881880970696</v>
       </c>
       <c r="D65" t="n">
-        <v>0.2336920280030381</v>
+        <v>0.2337598833068395</v>
       </c>
       <c r="E65" t="n">
         <v>0.3443000018596649</v>
@@ -1621,13 +1621,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.07703805612839545</v>
+        <v>0.07707461215471345</v>
       </c>
       <c r="C69" t="n">
         <v>0.1002773638328931</v>
       </c>
       <c r="D69" t="n">
-        <v>0.08279190443423591</v>
+        <v>0.08281936714647312</v>
       </c>
       <c r="E69" t="n">
         <v>0.1899999976158142</v>
@@ -1878,13 +1878,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.07232803956820501</v>
+        <v>0.07231954103867773</v>
       </c>
       <c r="C84" t="n">
         <v>0.05174930477244143</v>
       </c>
       <c r="D84" t="n">
-        <v>0.06451165932026172</v>
+        <v>0.06450679870079154</v>
       </c>
       <c r="E84" t="n">
         <v>0.1650000065565109</v>
@@ -2109,13 +2109,13 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.2438601733506817</v>
+        <v>0.2438620368154407</v>
       </c>
       <c r="C97" t="n">
         <v>0.2317778417147978</v>
       </c>
       <c r="D97" t="n">
-        <v>0.237760824316831</v>
+        <v>0.2377617611724428</v>
       </c>
       <c r="E97" t="n">
         <v>0.2780599892139435</v>
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.2336096422937053</v>
+        <v>0.2335987411080777</v>
       </c>
       <c r="C101" t="n">
         <v>0.287653639262351</v>
       </c>
       <c r="D101" t="n">
-        <v>0.2814869003994655</v>
+        <v>0.2814852442865994</v>
       </c>
       <c r="E101" t="n">
         <v>0.2973999977111816</v>
@@ -2266,13 +2266,13 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.169025474519205</v>
+        <v>0.1690112631072375</v>
       </c>
       <c r="C106" t="n">
         <v>0.3200277057737498</v>
       </c>
       <c r="D106" t="n">
-        <v>0.3002591490787528</v>
+        <v>0.3002558101775776</v>
       </c>
       <c r="E106" t="n">
         <v>0.2750000059604645</v>
@@ -2527,11 +2527,11 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.1813793395618107</v>
+        <v>0.1815977381625497</v>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="n">
-        <v>0.1813793395618107</v>
+        <v>0.1815977381625497</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
@@ -2663,11 +2663,11 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.05432787507761797</v>
+        <v>0.05432787408891399</v>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>0.05432787507761797</v>
+        <v>0.05432787408891399</v>
       </c>
       <c r="E129" t="n">
         <v>0.04999999914850507</v>
@@ -2680,11 +2680,11 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.1025110450004452</v>
+        <v>0.1026337101010628</v>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>0.1025110450004452</v>
+        <v>0.1026337101010628</v>
       </c>
       <c r="E130" t="n">
         <v>0.25</v>
@@ -2782,11 +2782,11 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.06832391353362346</v>
+        <v>0.07065404931153452</v>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="n">
-        <v>0.06832391353362346</v>
+        <v>0.07065404931153452</v>
       </c>
       <c r="E136" t="n">
         <v>0.1500000059604645</v>
@@ -2816,13 +2816,13 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.1748993645533501</v>
+        <v>0.1699769826454613</v>
       </c>
       <c r="C138" t="n">
         <v>0.2382269919199033</v>
       </c>
       <c r="D138" t="n">
-        <v>0.2206596457122175</v>
+        <v>0.2186369662564612</v>
       </c>
       <c r="E138" t="n">
         <v>0.239999994635582</v>
@@ -2848,548 +2848,548 @@
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>0.4855299165703345</v>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="n">
-        <v>0</v>
+        <v>0.4855299165703345</v>
       </c>
       <c r="E140" t="n">
-        <v>0.3</v>
+        <v>0.300000011920929</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>NIC</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4855249865226482</v>
+        <v>0.2665087291070496</v>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="n">
-        <v>0.4855249865226482</v>
+        <v>0.2665087291070496</v>
       </c>
       <c r="E141" t="n">
-        <v>0.300000011920929</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>NIC</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.2665087291070496</v>
-      </c>
-      <c r="C142" t="inlineStr"/>
+        <v>0.04244393892415248</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.1497323306832883</v>
+      </c>
       <c r="D142" t="n">
-        <v>0.2665087291070496</v>
+        <v>0.05532397703074036</v>
       </c>
       <c r="E142" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.04237689805304731</v>
+        <v>0.1907764539021621</v>
       </c>
       <c r="C143" t="n">
-        <v>0.1497323306832883</v>
+        <v>0.3601358491337873</v>
       </c>
       <c r="D143" t="n">
-        <v>0.05524752335770206</v>
+        <v>0.3329991717582893</v>
       </c>
       <c r="E143" t="n">
-        <v>0.25</v>
+        <v>0.2300000041723251</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>NPL</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.1907764539021621</v>
-      </c>
-      <c r="C144" t="n">
-        <v>0.3601358491337873</v>
-      </c>
+        <v>0.2688606979904855</v>
+      </c>
+      <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
-        <v>0.3329991717582893</v>
+        <v>0.2688606979904855</v>
       </c>
       <c r="E144" t="n">
-        <v>0.2300000041723251</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>NPL</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.2688606979904855</v>
-      </c>
-      <c r="C145" t="inlineStr"/>
+        <v>0.225694354493625</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0.2965583118215091</v>
+      </c>
       <c r="D145" t="n">
-        <v>0.2688606979904855</v>
+        <v>0.2376981831816407</v>
       </c>
       <c r="E145" t="n">
-        <v>0.2</v>
+        <v>0.2800000011920929</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>OAF</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.2256926192165145</v>
-      </c>
-      <c r="C146" t="n">
-        <v>0.2965583118215091</v>
-      </c>
+        <v>0.4375080724538686</v>
+      </c>
+      <c r="C146" t="inlineStr"/>
       <c r="D146" t="n">
-        <v>0.2376966651865194</v>
-      </c>
-      <c r="E146" t="n">
-        <v>0.2800000011920929</v>
-      </c>
+        <v>0.4375080724538686</v>
+      </c>
+      <c r="E146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>OAF</t>
+          <t>OAM</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4375080724538686</v>
+        <v>0.1223633536430578</v>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="n">
-        <v>0.4375080724538686</v>
+        <v>0.1223633536430578</v>
       </c>
       <c r="E147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>OAM</t>
+          <t>OAS</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.1223633536430578</v>
+        <v>0.2777941438266531</v>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="n">
-        <v>0.1223633536430578</v>
+        <v>0.2777941438266531</v>
       </c>
       <c r="E148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>OAS</t>
+          <t>OMN</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.2777941438266531</v>
+        <v>0.06242434485644292</v>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="n">
-        <v>0.2777941438266531</v>
-      </c>
-      <c r="E149" t="inlineStr"/>
+        <v>0.06242434485644292</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.1500000059604645</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>OMN</t>
+          <t>OTE</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.0664440588131273</v>
+        <v>0.09482803910884041</v>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="n">
-        <v>0.0664440588131273</v>
-      </c>
-      <c r="E150" t="n">
-        <v>0.1500000059604645</v>
-      </c>
+        <v>0.09482803910884041</v>
+      </c>
+      <c r="E150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>OTE</t>
+          <t>PAK</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.09482803910884041</v>
+        <v>0.5151554652034871</v>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="n">
-        <v>0.09482803910884041</v>
-      </c>
-      <c r="E151" t="inlineStr"/>
+        <v>0.5151554652034871</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>PAK</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5151554652034871</v>
+        <v>0.07547235932722365</v>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="n">
-        <v>0.5151554652034871</v>
+        <v>0.07547235932722365</v>
       </c>
       <c r="E152" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>PAN</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.07547235932722365</v>
-      </c>
-      <c r="C153" t="inlineStr"/>
+        <v>0.2707864102103573</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0.3071806584740951</v>
+      </c>
       <c r="D153" t="n">
-        <v>0.07547235932722365</v>
+        <v>0.2774485051153542</v>
       </c>
       <c r="E153" t="n">
-        <v>0.25</v>
+        <v>0.2949999868869781</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.2707864102103573</v>
-      </c>
-      <c r="C154" t="n">
-        <v>0.3071806584740951</v>
-      </c>
+        <v>0.2059146807764526</v>
+      </c>
+      <c r="C154" t="inlineStr"/>
       <c r="D154" t="n">
-        <v>0.2774485051153542</v>
+        <v>0.2059146807764526</v>
       </c>
       <c r="E154" t="n">
-        <v>0.2949999868869781</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>PLW</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.2059146807764526</v>
+        <v>0</v>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="n">
-        <v>0.2059146807764526</v>
+        <v>0</v>
       </c>
       <c r="E155" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>PLW</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0</v>
+        <v>0.08717504928998764</v>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>0.08717504928998764</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.08717504928998764</v>
+        <v>0.1633874774965221</v>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="n">
-        <v>0.08717504928998764</v>
+        <v>0.1633874774965221</v>
       </c>
       <c r="E157" t="n">
-        <v>0.3</v>
+        <v>0.1899999976158142</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>PRI</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.1633874774965221</v>
+        <v>0.0277049856528661</v>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="n">
-        <v>0.1633874774965221</v>
+        <v>0.0277049856528661</v>
       </c>
       <c r="E158" t="n">
-        <v>0.1899999976158142</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>PRI</t>
+          <t>PRK</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.0277049856528661</v>
+        <v>0.2225282195538792</v>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="n">
-        <v>0.0277049856528661</v>
+        <v>0.2225282195538792</v>
       </c>
       <c r="E159" t="n">
-        <v>0.39</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>PRK</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.2225282195538792</v>
+        <v>0.1567103663703431</v>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="n">
-        <v>0.2225282195538792</v>
+        <v>0.1567103663703431</v>
       </c>
       <c r="E160" t="n">
-        <v>0.325</v>
+        <v>0.3149999976158142</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>PRY</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.1567103663703431</v>
+        <v>0.09209368580212636</v>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="n">
-        <v>0.1567103663703431</v>
+        <v>0.09209368580212636</v>
       </c>
       <c r="E161" t="n">
-        <v>0.3149999976158142</v>
+        <v>0.1000000014901161</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>PRY</t>
+          <t>QAT</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.09209368580212636</v>
+        <v>0.2923752830465065</v>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="n">
-        <v>0.09209368580212636</v>
+        <v>0.2923752830465065</v>
       </c>
       <c r="E162" t="n">
-        <v>0.1000000014901161</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>QAT</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.2923752830465065</v>
-      </c>
-      <c r="C163" t="inlineStr"/>
+        <v>0.1504646594497204</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0.1176429300358615</v>
+      </c>
       <c r="D163" t="n">
-        <v>0.2923752830465065</v>
+        <v>0.1475405164005239</v>
       </c>
       <c r="E163" t="n">
-        <v>0.1</v>
+        <v>0.1599999964237213</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.1504646594497204</v>
-      </c>
-      <c r="C164" t="n">
-        <v>0.1176429300358615</v>
-      </c>
+        <v>0.2312696107253581</v>
+      </c>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" t="n">
-        <v>0.1475405164005239</v>
+        <v>0.2312696107253581</v>
       </c>
       <c r="E164" t="n">
-        <v>0.1599999964237213</v>
+        <v>0.2000000029802322</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.2312696107253581</v>
+        <v>0</v>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="n">
-        <v>0.2312696107253581</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
-        <v>0.2000000029802322</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>SAU</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0</v>
-      </c>
-      <c r="C166" t="inlineStr"/>
+        <v>0.06693206506565626</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0.6614591322779771</v>
+      </c>
       <c r="D166" t="n">
         <v>0</v>
       </c>
       <c r="E166" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>SAU</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.06693205965292903</v>
-      </c>
-      <c r="C167" t="n">
-        <v>0.6614591322779771</v>
-      </c>
+        <v>0.03042192258350664</v>
+      </c>
+      <c r="C167" t="inlineStr"/>
       <c r="D167" t="n">
-        <v>0</v>
+        <v>0.03042192258350664</v>
       </c>
       <c r="E167" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>SEN</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.03042192258350664</v>
+        <v>0.2416996317414143</v>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="n">
-        <v>0.03042192258350664</v>
+        <v>0.2416996317414143</v>
       </c>
       <c r="E168" t="n">
-        <v>0.35</v>
+        <v>0.300000011920929</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>SEN</t>
+          <t>SGP</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.2416996317414143</v>
-      </c>
-      <c r="C169" t="inlineStr"/>
+        <v>0.07628740368318995</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0.1896598339380842</v>
+      </c>
       <c r="D169" t="n">
-        <v>0.2416996317414143</v>
+        <v>0.09571020682046806</v>
       </c>
       <c r="E169" t="n">
-        <v>0.300000011920929</v>
+        <v>0.1700000017881393</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>SGP</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.07631584368089703</v>
-      </c>
-      <c r="C170" t="n">
-        <v>0.1896598339380842</v>
-      </c>
+        <v>0.1875691135730537</v>
+      </c>
+      <c r="C170" t="inlineStr"/>
       <c r="D170" t="n">
-        <v>0.09572735811429038</v>
+        <v>0.1875691135730537</v>
       </c>
       <c r="E170" t="n">
-        <v>0.1700000017881393</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>SLE</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.1875691135730537</v>
+        <v>0.5125783914217011</v>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="n">
-        <v>0.1875691135730537</v>
+        <v>0.5125783914217011</v>
       </c>
       <c r="E171" t="n">
         <v>0.3</v>
@@ -3398,15 +3398,15 @@
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.5125783914217011</v>
+        <v>0.2335880037024277</v>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="n">
-        <v>0.5125783914217011</v>
+        <v>0.2335880037024277</v>
       </c>
       <c r="E172" t="n">
         <v>0.3</v>
@@ -3415,272 +3415,272 @@
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>SRB</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.2335880037024277</v>
+        <v>0.04284709281051042</v>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="n">
-        <v>0.2335880037024277</v>
+        <v>0.04284709281051042</v>
       </c>
       <c r="E173" t="n">
-        <v>0.3</v>
+        <v>0.1500000059604645</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>SRB</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.04284709281051042</v>
+        <v>0.1729177704997241</v>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="n">
-        <v>0.04284709281051042</v>
+        <v>0.1729177704997241</v>
       </c>
       <c r="E174" t="n">
-        <v>0.1500000059604645</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.1729177704997241</v>
+        <v>0.01020667011658059</v>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="n">
-        <v>0.1729177704997241</v>
-      </c>
-      <c r="E175" t="n">
-        <v>0.25</v>
-      </c>
+        <v>0.01020667011658059</v>
+      </c>
+      <c r="E175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>SUR</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.01020537519950413</v>
+        <v>0.3190768722555981</v>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="n">
-        <v>0.01020537519950413</v>
-      </c>
-      <c r="E176" t="inlineStr"/>
+        <v>0.3190768722555981</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0.36</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>SUR</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.3190768722555981</v>
+        <v>0.2303916416929371</v>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="n">
-        <v>0.3190768722555981</v>
+        <v>0.2303916416929371</v>
       </c>
       <c r="E177" t="n">
-        <v>0.36</v>
+        <v>0.2099999934434891</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.2303916416929371</v>
-      </c>
-      <c r="C178" t="inlineStr"/>
+        <v>0.1459344076588751</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.1451565963133123</v>
+      </c>
       <c r="D178" t="n">
-        <v>0.2303916416929371</v>
+        <v>0.1455317416108768</v>
       </c>
       <c r="E178" t="n">
-        <v>0.2099999934434891</v>
+        <v>0.1899999976158142</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.1459344076588751</v>
+        <v>0.1471577486317217</v>
       </c>
       <c r="C179" t="n">
-        <v>0.1451565963133123</v>
+        <v>0.2000509994614199</v>
       </c>
       <c r="D179" t="n">
-        <v>0.1455317416108768</v>
+        <v>0.1779765147101586</v>
       </c>
       <c r="E179" t="n">
-        <v>0.1899999976158142</v>
+        <v>0.2199999988079071</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.1471577486317217</v>
-      </c>
-      <c r="C180" t="n">
-        <v>0.2000509994614199</v>
-      </c>
+        <v>0.08222621854106736</v>
+      </c>
+      <c r="C180" t="inlineStr"/>
       <c r="D180" t="n">
-        <v>0.1779765147101586</v>
+        <v>0.08222621854106736</v>
       </c>
       <c r="E180" t="n">
-        <v>0.2199999988079071</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>SXM</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.08222621854106736</v>
+        <v>0</v>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="n">
-        <v>0.08222621854106736</v>
+        <v>0</v>
       </c>
       <c r="E181" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>SXM</t>
+          <t>SYC</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0</v>
+        <v>8.096728096899197e-06</v>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="n">
-        <v>0</v>
+        <v>8.096728096899197e-06</v>
       </c>
       <c r="E182" t="n">
-        <v>0.35</v>
+        <v>0.300000011920929</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>SYC</t>
+          <t>TGO</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>8.019693542794952e-06</v>
+        <v>0.1315378116244645</v>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="n">
-        <v>8.019693542794952e-06</v>
+        <v>0.1315378116244645</v>
       </c>
       <c r="E183" t="n">
-        <v>0.300000011920929</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>TGO</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.1315378116244645</v>
+        <v>0.1752951760081964</v>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="n">
-        <v>0.1315378116244645</v>
+        <v>0.1752951760081964</v>
       </c>
       <c r="E184" t="n">
-        <v>0.175</v>
+        <v>0.2000000029802322</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>TJK</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.1752951759973909</v>
+        <v>0</v>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="n">
-        <v>0.1752951759973909</v>
+        <v>0</v>
       </c>
       <c r="E185" t="n">
-        <v>0.2000000029802322</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>TJK</t>
+          <t>TLS</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0</v>
+        <v>0.006253579230815983</v>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="n">
-        <v>0</v>
+        <v>0.006253579230815983</v>
       </c>
       <c r="E186" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>TTO</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.09206882827985034</v>
+        <v>0.3456741791627991</v>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="n">
-        <v>0.09206882827985034</v>
+        <v>0.3456741791627991</v>
       </c>
       <c r="E187" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>TTO</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.3456741791627991</v>
+        <v>0.25</v>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="n">
-        <v>0.3456741791627991</v>
+        <v>0.25</v>
       </c>
       <c r="E188" t="n">
         <v>0.25</v>
@@ -3689,66 +3689,66 @@
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>TUR</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.25</v>
+        <v>0.2114292236825039</v>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="n">
-        <v>0.25</v>
+        <v>0.2114292236825039</v>
       </c>
       <c r="E189" t="n">
-        <v>0.25</v>
+        <v>0.2199999988079071</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>TUR</t>
+          <t>TWN</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.2114292236825039</v>
+        <v>0.1602917818562184</v>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="n">
-        <v>0.2114292236825039</v>
+        <v>0.1602917818562184</v>
       </c>
       <c r="E190" t="n">
-        <v>0.2199999988079071</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>TWN</t>
+          <t>TZA</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.1602917818562184</v>
+        <v>0.4303901408412513</v>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="n">
-        <v>0.1602917818562184</v>
+        <v>0.4303901408412513</v>
       </c>
       <c r="E191" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>TZA</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.4303901408412513</v>
+        <v>0.1742779067138577</v>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="n">
-        <v>0.4303901408412513</v>
+        <v>0.1742779067138577</v>
       </c>
       <c r="E192" t="n">
         <v>0.3</v>
@@ -3757,291 +3757,274 @@
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.1742779067138577</v>
+        <v>0.4688492025488057</v>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="n">
-        <v>0.1742779067138577</v>
+        <v>0.4688492025488057</v>
       </c>
       <c r="E193" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>URY</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.4688492025488057</v>
+        <v>0.0896334695691004</v>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="n">
-        <v>0.4688492025488057</v>
+        <v>0.0896334695691004</v>
       </c>
       <c r="E194" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>URY</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.0896334695691004</v>
-      </c>
-      <c r="C195" t="inlineStr"/>
+        <v>0.09197646954365848</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.3085010944592488</v>
+      </c>
       <c r="D195" t="n">
-        <v>0.0896334695691004</v>
+        <v>0.2279795048093673</v>
       </c>
       <c r="E195" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UZB</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.09197695807867363</v>
-      </c>
-      <c r="C196" t="n">
-        <v>0.3085010944592488</v>
-      </c>
+        <v>0.02101704879482657</v>
+      </c>
+      <c r="C196" t="inlineStr"/>
       <c r="D196" t="n">
-        <v>0.2279799551263891</v>
+        <v>0.02101704879482657</v>
       </c>
       <c r="E196" t="n">
-        <v>0.27</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>UZB</t>
+          <t>VCT</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.02101704879482657</v>
+        <v>0.0759328257677378</v>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="n">
-        <v>0.02101704879482657</v>
+        <v>0.0759328257677378</v>
       </c>
       <c r="E197" t="n">
-        <v>0.075</v>
+        <v>0.300000011920929</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>VCT</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.0759328257677378</v>
+        <v>0.0245751095953905</v>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="n">
-        <v>0.0759328257677378</v>
+        <v>0.0245751095953905</v>
       </c>
       <c r="E198" t="n">
-        <v>0.300000011920929</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>VEN</t>
+          <t>VGB</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.0245751095953905</v>
+        <v>0.004545591728540787</v>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="n">
-        <v>0.0245751095953905</v>
+        <v>0.004545591728540787</v>
       </c>
       <c r="E199" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>VGB</t>
+          <t>VIR</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.004556701568063922</v>
+        <v>0.002348810686027111</v>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="n">
-        <v>0.004556701568063922</v>
+        <v>0.002348810686027111</v>
       </c>
       <c r="E200" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>VIR</t>
+          <t>VNM</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.002047370511032536</v>
+        <v>0.1556271219162854</v>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="n">
-        <v>0.002047370511032536</v>
+        <v>0.1556271219162854</v>
       </c>
       <c r="E201" t="n">
-        <v>0.231</v>
+        <v>0.2000000029802322</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>VNM</t>
+          <t>VUT</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.1556245797252942</v>
+        <v>0.002850910551829294</v>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="n">
-        <v>0.1556245797252942</v>
+        <v>0.002850910551829294</v>
       </c>
       <c r="E202" t="n">
-        <v>0.2000000029802322</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>VUT</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.002850910551829294</v>
+        <v>0.0561499795539249</v>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="n">
-        <v>0.002850910551829294</v>
+        <v>0.0561499795539249</v>
       </c>
       <c r="E203" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>XKV</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.0561499795539249</v>
+        <v>0.07844905320108206</v>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="n">
-        <v>0.0561499795539249</v>
-      </c>
-      <c r="E204" t="n">
-        <v>0.27</v>
-      </c>
+        <v>0.07844905320108206</v>
+      </c>
+      <c r="E204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>XKV</t>
+          <t>YEM</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.07844905320108206</v>
+        <v>0.0869715567000066</v>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="n">
-        <v>0.07844905320108206</v>
-      </c>
-      <c r="E205" t="inlineStr"/>
+        <v>0.0869715567000066</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>YEM</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.09232172972302595</v>
-      </c>
-      <c r="C206" t="inlineStr"/>
+        <v>0.2409344214009213</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.1573130452526269</v>
+      </c>
       <c r="D206" t="n">
-        <v>0.09232172972302595</v>
+        <v>0.1794950348715632</v>
       </c>
       <c r="E206" t="n">
-        <v>0.2</v>
+        <v>0.2800000011920929</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>ZMB</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.2409258346327973</v>
-      </c>
-      <c r="C207" t="n">
-        <v>0.1573130452526269</v>
-      </c>
+        <v>0.3414888896353339</v>
+      </c>
+      <c r="C207" t="inlineStr"/>
       <c r="D207" t="n">
-        <v>0.1794927512243368</v>
+        <v>0.3414888896353339</v>
       </c>
       <c r="E207" t="n">
-        <v>0.2800000011920929</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>ZMB</t>
+          <t>ZWE</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.3414888896353339</v>
+        <v>0.1434566666525137</v>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="n">
-        <v>0.3414888896353339</v>
+        <v>0.1434566666525137</v>
       </c>
       <c r="E208" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="1" t="inlineStr">
-        <is>
-          <t>ZWE</t>
-        </is>
-      </c>
-      <c r="B209" t="n">
-        <v>0.1434566666525137</v>
-      </c>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="n">
-        <v>0.1434566666525137</v>
-      </c>
-      <c r="E209" t="n">
         <v>0.25</v>
       </c>
     </row>
